--- a/figures/supporting_information/S3_Table.xlsx
+++ b/figures/supporting_information/S3_Table.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity analyses" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Additional checks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -831,4 +832,186 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>One model per patient (smallest ModelID)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1146 models; 89 candidates; 87 of 94 retained; not retained: CUL2 (cervix); FAM50A (bladder/urinary tract); NCAPD3 (eye); SCD (bowel); SDHB (myeloid); SOX10 (eye); TUBB4B (ampulla of vater)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Patient-block label permutation (1,000)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mean 0.00, max 0 prioritised pairs; max 2 pairs with q &lt; 0.05; empirical p = 0.0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Welch t-test, BH over all tests</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>85 of 94 with q &lt; 0.05 and negative mean difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Permutation p (10,000), FOXA1 prostate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>n = 5; asymptotic p = 0.00078; permutation p = 0.0006</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Permutation p (10,000), TUBB4B ampulla of vater</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>n = 5; asymptotic p = 0.001; permutation p = 0.0007</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Permutation p (10,000), DCAF7 myeloid</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>n = 7; asymptotic p = 0.00084; permutation p = 0.0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Batch/library-adjusted coefficients (94 pairs, post-selection)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>95% CI below 0 for 94 pairs; minimum ratio adjusted/unadjusted 0.75 (batch_coef_ci.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MDM2 eye, no detected TP53 variant only</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n = 9; selectivity -0.36; p = 0.021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MDM2 kidney, no detected TP53 variant only</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>n = 25; selectivity -0.24; p = 0.0029</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MDM2 pleura, no detected TP53 variant only</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>n = 17; selectivity -0.14; p = 0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MDM2 skin, no detected TP53 variant only</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>n = 47; selectivity -0.55; p = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Within-lineage co-dependency, matched null (1,000 sets)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>observed median |r| 0.39; null mean 0.05, max 0.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>22Q1 vs 26Q1 on the same 1,036 models</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>primary pairs meeting the rule: 84 (26Q1 data) vs 23 (22Q1 data)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/figures/supporting_information/S3_Table.xlsx
+++ b/figures/supporting_information/S3_Table.xlsx
@@ -983,7 +983,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>n = 47; selectivity -0.55; p = 0</t>
+          <t>n = 47; selectivity -0.55; p = 1.4e-07</t>
         </is>
       </c>
     </row>

--- a/figures/supporting_information/S3_Table.xlsx
+++ b/figures/supporting_information/S3_Table.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,10 +1002,166 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Growth-pattern adjustment of the 42 blood pairs, with / without the other blood lineage</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>median ratio adjusted/unadjusted 0.56 / 0.84; pairs with q &lt; 0.05 36 / 42 (growth_confound_pairs.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sanger replication by lineage group</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lymphoid 16/17, other 8/15; non-prioritised reference 294/1182 and 263/1079; failing only the median criterion 18/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bootstrap 95% intervals of selectivity (1,000 resamples, seed 42; per pair in S2 Table)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>entirely below -0.5: 29 pairs (seeds 43-45: 28, 28, 28); below 0: 93</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Median of all other lines, prioritised pairs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>above -0.5: 40; -1 to -0.5: 41; -1 or below: 13; another eligible lineage below -1: 74</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Non-blood pairs with other comparison groups (selectivity &lt; -0.5, of 52)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>adherent lines only 42; without suspension lines 45; without blood lines 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CTNNB1 by APC truncating variant</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>median -1.04 (n = 78) vs -0.13 (n = 1023); lineage-adjusted difference -0.54, p = 5.7e-26; within lineage -1.34 (n = 49) vs -0.52 (n = 9), p = 0.011</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BRAF by BRAF V600 variant</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>median -1.20 (n = 79) vs -0.08 (n = 1067); lineage-adjusted difference -0.97, p = 4.2e-135; within lineage -1.28 (n = 49) vs -0.09 (n = 23), p = 4.8e-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CTNNB1 in bowel by APC/CTNNB1 group</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>APC truncating -1.34 (n = 49); CTNNB1 hotspot -1.76 (n = 4); neither -0.36 (n = 8) vs other lineages -0.13, p = 0.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lineage coefficient adjusted for genotype, KRAS pancreas</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ratio 0.28 (p = 6.9e-10); interaction model: lineage effect in non-carriers -0.03 (p = 0.91), lineage x genotype -0.43 (p = 0.082)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lineage coefficient adjusted for genotype, CTNNB1 bowel</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ratio 0.50 (p = 3.1e-21); interaction model: lineage effect in non-carriers -0.52 (p = 3.3e-06), lineage x genotype 0.01 (p = 0.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Lineage coefficient adjusted for genotype, BRAF skin</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ratio 0.22 (p = 2.8e-08); interaction model: lineage effect in non-carriers -0.05 (p = 0.29), lineage x genotype -0.31 (p = 4e-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Lineage coefficient adjusted for genotype, BRAF skin without engineered</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ratio 0.27 (p = 2.1e-12); interaction model: lineage effect in non-carriers -0.05 (p = 0.27), lineage x genotype -0.43 (p = 9.9e-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>22Q1 with quantile-matched thresholds (shared lines)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>selectivity -0.41, median -1.05: 31 of 90 pairs meet the rule; selectivity only: 37; original thresholds: 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>22Q1 vs 26Q1 on the same 1,036 models</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>primary pairs meeting the rule: 84 (26Q1 data) vs 23 (22Q1 data)</t>
         </is>

--- a/figures/supporting_information/S3_Table.xlsx
+++ b/figures/supporting_information/S3_Table.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,10 +1158,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>RNAi screens (DEMETER2), prioritised pairs</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>32 of 81 testable pairs with q &lt; 0.05 and negative selectivity; reference 749/7871; high/medium/low confidence 10/18, 13/36, 9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>22Q1 vs 26Q1 on the same 1,036 models</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>primary pairs meeting the rule: 84 (26Q1 data) vs 23 (22Q1 data)</t>
         </is>

--- a/figures/supporting_information/S3_Table.xlsx
+++ b/figures/supporting_information/S3_Table.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32 of 81 testable pairs with q &lt; 0.05 and negative selectivity; reference 749/7871; high/medium/low confidence 10/18, 13/36, 9/27</t>
+          <t>32 of 81 testable pairs with q &lt; 0.05 and negative selectivity; reference 750/7871; high/medium/low confidence 10/18, 13/36, 9/27</t>
         </is>
       </c>
     </row>

--- a/figures/supporting_information/S3_Table.xlsx
+++ b/figures/supporting_information/S3_Table.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32 of 81 testable pairs with q &lt; 0.05 and negative selectivity; reference 750/7871; high/medium/low confidence 10/18, 13/36, 9/27</t>
+          <t>32 of 81 testable pairs with q &lt; 0.05 and negative selectivity; reference 750/7871; high/medium/low robustness tier 10/18, 13/36, 9/27</t>
         </is>
       </c>
     </row>

--- a/figures/supporting_information/S3_Table.xlsx
+++ b/figures/supporting_information/S3_Table.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>median ratio adjusted/unadjusted 0.56 / 0.84; pairs with q &lt; 0.05 36 / 42 (growth_confound_pairs.csv)</t>
+          <t>median ratio adjusted/unadjusted 0.56 / 0.84; pairs with q &lt; 0.05 35 / 42 (growth_confound_pairs.csv)</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>median -1.04 (n = 78) vs -0.13 (n = 1023); lineage-adjusted difference -0.54, p = 5.7e-26; within lineage -1.34 (n = 49) vs -0.52 (n = 9), p = 0.011</t>
+          <t>median -1.04 (n = 78) vs -0.13 (n = 1023); lineage-adjusted difference -0.54, p = 8.9e-07; within lineage -1.34 (n = 49) vs -0.52 (n = 9), p = 0.011</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>median -1.20 (n = 79) vs -0.08 (n = 1067); lineage-adjusted difference -0.97, p = 4.2e-135; within lineage -1.28 (n = 49) vs -0.09 (n = 23), p = 4.8e-11</t>
+          <t>median -1.20 (n = 79) vs -0.08 (n = 1067); lineage-adjusted difference -0.97, p = 6.7e-43; within lineage -1.28 (n = 49) vs -0.09 (n = 23), p = 4.8e-11</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ratio 0.28 (p = 6.9e-10); interaction model: lineage effect in non-carriers -0.03 (p = 0.91), lineage x genotype -0.43 (p = 0.082)</t>
+          <t>ratio 0.28 (p = 0.0026); interaction model: lineage effect in non-carriers -0.03 (p = 0.91), lineage x genotype -0.43 (p = 0.14)</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ratio 0.50 (p = 3.1e-21); interaction model: lineage effect in non-carriers -0.52 (p = 3.3e-06), lineage x genotype 0.01 (p = 0.93)</t>
+          <t>ratio 0.50 (p = 2.6e-05); interaction model: lineage effect in non-carriers -0.52 (p = 0.11), lineage x genotype 0.01 (p = 0.98)</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ratio 0.22 (p = 2.8e-08); interaction model: lineage effect in non-carriers -0.05 (p = 0.29), lineage x genotype -0.31 (p = 4e-06)</t>
+          <t>ratio 0.22 (p = 0.0012); interaction model: lineage effect in non-carriers -0.05 (p = 0.17), lineage x genotype -0.31 (p = 0.0096)</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ratio 0.27 (p = 2.1e-12); interaction model: lineage effect in non-carriers -0.05 (p = 0.27), lineage x genotype -0.43 (p = 9.9e-11)</t>
+          <t>ratio 0.27 (p = 6e-05); interaction model: lineage effect in non-carriers -0.05 (p = 0.17), lineage x genotype -0.43 (p = 0.00029)</t>
         </is>
       </c>
     </row>
